--- a/output/site_info_clean.xlsx
+++ b/output/site_info_clean.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J905"/>
+  <dimension ref="A1:J929"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -11136,7 +11136,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -12096,7 +12096,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -13816,7 +13816,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -13846,7 +13846,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -13876,7 +13876,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -13906,7 +13906,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -13966,7 +13966,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -13996,7 +13996,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -14996,7 +14996,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père2</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -15016,7 +15016,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père2</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père2</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père2</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père2</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -15096,7 +15096,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père2</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père2</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père2</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père2</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
@@ -15396,7 +15396,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
@@ -15436,7 +15436,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
@@ -15476,7 +15476,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
@@ -15496,7 +15496,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
@@ -15516,7 +15516,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
@@ -15536,7 +15536,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
@@ -15556,7 +15556,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
@@ -15596,7 +15596,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
@@ -16711,7 +16711,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -16741,7 +16741,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -16771,7 +16771,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -16801,7 +16801,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -16831,7 +16831,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -16861,7 +16861,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -16891,7 +16891,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -16921,7 +16921,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -16951,7 +16951,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -16981,7 +16981,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -18231,7 +18231,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -18261,7 +18261,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -18321,7 +18321,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -18351,7 +18351,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -18381,7 +18381,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -18411,7 +18411,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -18471,7 +18471,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -18501,7 +18501,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="F672" t="inlineStr">
@@ -23784,7 +23784,7 @@
           <t>Grande parcelle</t>
         </is>
       </c>
-      <c r="C878" t="inlineStr">
+      <c r="D878" t="inlineStr">
         <is>
           <t>70</t>
         </is>
@@ -23809,7 +23809,7 @@
           <t>Grande parcelle</t>
         </is>
       </c>
-      <c r="C879" t="inlineStr">
+      <c r="D879" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -23834,7 +23834,7 @@
           <t>Grande parcelle</t>
         </is>
       </c>
-      <c r="C880" t="inlineStr">
+      <c r="D880" t="inlineStr">
         <is>
           <t>55</t>
         </is>
@@ -23859,7 +23859,7 @@
           <t>Grande parcelle</t>
         </is>
       </c>
-      <c r="C881" t="inlineStr">
+      <c r="D881" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -23870,6 +23870,26 @@
         </is>
       </c>
       <c r="F881" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882">
+        <v>2026</v>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Grande parcelle</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -23975,6 +23995,106 @@
         </is>
       </c>
     </row>
+    <row r="887">
+      <c r="A887">
+        <v>2026</v>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Grande parcelle</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888">
+        <v>2026</v>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Grande parcelle</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889">
+        <v>2026</v>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Grande parcelle</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890">
+        <v>2026</v>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Grande parcelle</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
     <row r="891">
       <c r="A891">
         <v>2026</v>
@@ -24195,6 +24315,31 @@
         </is>
       </c>
     </row>
+    <row r="900">
+      <c r="A900">
+        <v>2026</v>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
     <row r="901">
       <c r="A901">
         <v>2026</v>
@@ -24209,6 +24354,16 @@
           <t>80</t>
         </is>
       </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
     </row>
     <row r="902">
       <c r="A902">
@@ -24224,6 +24379,16 @@
           <t>60</t>
         </is>
       </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
     </row>
     <row r="903">
       <c r="A903">
@@ -24239,6 +24404,16 @@
           <t>55</t>
         </is>
       </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
     </row>
     <row r="904">
       <c r="A904">
@@ -24254,6 +24429,16 @@
           <t>65</t>
         </is>
       </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
     </row>
     <row r="905">
       <c r="A905">
@@ -24267,6 +24452,576 @@
       <c r="D905" t="inlineStr">
         <is>
           <t>70</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906">
+        <v>2026</v>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907">
+        <v>2026</v>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908">
+        <v>2026</v>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909">
+        <v>2026</v>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910">
+        <v>2026</v>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911">
+        <v>2026</v>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Gîte</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912">
+        <v>2026</v>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913">
+        <v>2026</v>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914">
+        <v>2026</v>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915">
+        <v>2026</v>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916">
+        <v>2026</v>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917">
+        <v>2026</v>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918">
+        <v>2026</v>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919">
+        <v>2026</v>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920">
+        <v>2026</v>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Gite</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921">
+        <v>2026</v>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922">
+        <v>2026</v>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923">
+        <v>2026</v>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924">
+        <v>2026</v>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925">
+        <v>2026</v>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926">
+        <v>2026</v>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927">
+        <v>2026</v>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928">
+        <v>2026</v>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929">
+        <v>2026</v>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>FP</t>
         </is>
       </c>
     </row>

--- a/output/site_info_clean.xlsx
+++ b/output/site_info_clean.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J905"/>
+  <dimension ref="A1:J953"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -11136,7 +11136,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -12096,7 +12096,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -13816,7 +13816,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -13846,7 +13846,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -13876,7 +13876,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -13906,7 +13906,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -13966,7 +13966,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -13996,7 +13996,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -14996,7 +14996,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père 2</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -15016,7 +15016,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père 2</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père 2</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père 2</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père 2</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -15096,7 +15096,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père 2</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père 2</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père 2</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père 2</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
@@ -15396,7 +15396,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
@@ -15436,7 +15436,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
@@ -15476,7 +15476,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
@@ -15496,7 +15496,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
@@ -15516,7 +15516,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
@@ -15536,7 +15536,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
@@ -15556,7 +15556,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
@@ -15596,7 +15596,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
@@ -16711,7 +16711,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -16741,7 +16741,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -16771,7 +16771,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -16801,7 +16801,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -16831,7 +16831,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -16861,7 +16861,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -16891,7 +16891,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -16921,7 +16921,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -16951,7 +16951,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -16981,7 +16981,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -18231,7 +18231,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -18261,7 +18261,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -18321,7 +18321,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -18351,7 +18351,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -18381,7 +18381,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -18411,7 +18411,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -18471,7 +18471,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -18501,7 +18501,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="F672" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -22291,7 +22291,7 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -22341,7 +22341,7 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -22366,7 +22366,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -22391,7 +22391,7 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -22416,7 +22416,7 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="F825" t="inlineStr">
@@ -22431,7 +22431,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="F826" t="inlineStr">
@@ -22446,7 +22446,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="F827" t="inlineStr">
@@ -22461,7 +22461,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="F828" t="inlineStr">
@@ -22476,7 +22476,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="F829" t="inlineStr">
@@ -22491,7 +22491,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="F830" t="inlineStr">
@@ -22506,7 +22506,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="F831" t="inlineStr">
@@ -23784,7 +23784,7 @@
           <t>Grande parcelle</t>
         </is>
       </c>
-      <c r="C878" t="inlineStr">
+      <c r="D878" t="inlineStr">
         <is>
           <t>70</t>
         </is>
@@ -23809,7 +23809,7 @@
           <t>Grande parcelle</t>
         </is>
       </c>
-      <c r="C879" t="inlineStr">
+      <c r="D879" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -23834,7 +23834,7 @@
           <t>Grande parcelle</t>
         </is>
       </c>
-      <c r="C880" t="inlineStr">
+      <c r="D880" t="inlineStr">
         <is>
           <t>55</t>
         </is>
@@ -23859,7 +23859,7 @@
           <t>Grande parcelle</t>
         </is>
       </c>
-      <c r="C881" t="inlineStr">
+      <c r="D881" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -23870,6 +23870,26 @@
         </is>
       </c>
       <c r="F881" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882">
+        <v>2026</v>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Grande parcelle</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -23975,13 +23995,113 @@
         </is>
       </c>
     </row>
+    <row r="887">
+      <c r="A887">
+        <v>2026</v>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Grande parcelle</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888">
+        <v>2026</v>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Grande parcelle</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889">
+        <v>2026</v>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Grande parcelle</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890">
+        <v>2026</v>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Grande parcelle</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
     <row r="891">
       <c r="A891">
         <v>2026</v>
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D891" t="inlineStr">
@@ -24006,7 +24126,7 @@
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D892" t="inlineStr">
@@ -24031,7 +24151,7 @@
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D893" t="inlineStr">
@@ -24056,7 +24176,7 @@
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
@@ -24081,7 +24201,7 @@
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
@@ -24106,7 +24226,7 @@
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
@@ -24131,7 +24251,7 @@
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
@@ -24156,7 +24276,7 @@
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="E898" t="inlineStr">
@@ -24195,18 +24315,53 @@
         </is>
       </c>
     </row>
+    <row r="900">
+      <c r="A900">
+        <v>2026</v>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
     <row r="901">
       <c r="A901">
         <v>2026</v>
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
         <is>
           <t>80</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>FP</t>
         </is>
       </c>
     </row>
@@ -24216,12 +24371,22 @@
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
         <is>
           <t>60</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>FP</t>
         </is>
       </c>
     </row>
@@ -24231,12 +24396,22 @@
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
         <is>
           <t>55</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>FP</t>
         </is>
       </c>
     </row>
@@ -24246,12 +24421,22 @@
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
         <is>
           <t>65</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>FP</t>
         </is>
       </c>
     </row>
@@ -24261,12 +24446,1227 @@
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
         <is>
           <t>70</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906">
+        <v>2026</v>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907">
+        <v>2026</v>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908">
+        <v>2026</v>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909">
+        <v>2026</v>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910">
+        <v>2026</v>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911">
+        <v>2026</v>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Gite</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912">
+        <v>2026</v>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913">
+        <v>2026</v>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914">
+        <v>2026</v>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915">
+        <v>2026</v>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916">
+        <v>2026</v>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917">
+        <v>2026</v>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918">
+        <v>2026</v>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919">
+        <v>2026</v>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920">
+        <v>2026</v>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Gite</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921">
+        <v>2026</v>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922">
+        <v>2026</v>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923">
+        <v>2026</v>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924">
+        <v>2026</v>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925">
+        <v>2026</v>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926">
+        <v>2026</v>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927">
+        <v>2026</v>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928">
+        <v>2026</v>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929">
+        <v>2026</v>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930">
+        <v>2026</v>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>Mesnil st père</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931">
+        <v>2026</v>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>Mesnil st père</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932">
+        <v>2026</v>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Mesnil st père</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933">
+        <v>2026</v>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Mesnil st père</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934">
+        <v>2026</v>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Mesnil st père</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935">
+        <v>2026</v>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>Mesnil st père</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936">
+        <v>2026</v>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>Mesnil st père</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937">
+        <v>2026</v>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>Mesnil st père</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="J937" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938">
+        <v>2026</v>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Mesnil st père</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939">
+        <v>2026</v>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>Mesnil st père</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940">
+        <v>2026</v>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>Mesnil st père</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941">
+        <v>2026</v>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>Mesnil st père</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942">
+        <v>2026</v>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>Mesnil st père 2</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943">
+        <v>2026</v>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>Mesnil st père 2</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944">
+        <v>2026</v>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>Mesnil st père 2</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945">
+        <v>2026</v>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>Mesnil st père 2</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946">
+        <v>2026</v>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>Mesnil st père 2</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947">
+        <v>2026</v>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>Mesnil st père 2</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948">
+        <v>2026</v>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Mesnil st père 2</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949">
+        <v>2026</v>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Mesnil st père 2</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950">
+        <v>2026</v>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>Mesnil st père 2</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951">
+        <v>2026</v>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>Mesnil st père 2</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952">
+        <v>2026</v>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>Mesnil st père 2</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953">
+        <v>2026</v>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>Mesnil st père 2</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>FT</t>
         </is>
       </c>
     </row>

--- a/output/site_info_clean.xlsx
+++ b/output/site_info_clean.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J905"/>
+  <dimension ref="A1:J929"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -382,7 +382,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Mode_de_gestion</t>
+          <t>Mode_de_gestion</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -7746,7 +7746,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Grande Parcelle</t>
+          <t>Grande parcelle</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -10806,7 +10806,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -11016,7 +11016,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -11136,7 +11136,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -12096,7 +12096,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -12136,7 +12136,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -12176,7 +12176,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
@@ -12236,7 +12236,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
@@ -13726,7 +13726,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -13816,7 +13816,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -13846,7 +13846,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -13876,7 +13876,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -13906,7 +13906,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -13966,7 +13966,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -13996,7 +13996,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -14026,7 +14026,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -14996,7 +14996,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père2</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -15016,7 +15016,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père2</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père2</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père2</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père2</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -15096,7 +15096,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père2</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père2</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père2</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Mesnil st pere2</t>
+          <t>Mesnil st père2</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
@@ -15396,7 +15396,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
@@ -15436,7 +15436,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
@@ -15456,7 +15456,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
@@ -15476,7 +15476,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
@@ -15496,7 +15496,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
@@ -15516,7 +15516,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
@@ -15536,7 +15536,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
@@ -15556,7 +15556,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
@@ -15596,7 +15596,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
@@ -16711,7 +16711,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
@@ -16741,7 +16741,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C614" t="inlineStr">
@@ -16771,7 +16771,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
@@ -16801,7 +16801,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
@@ -16831,7 +16831,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
@@ -16861,7 +16861,7 @@
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
@@ -16891,7 +16891,7 @@
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C619" t="inlineStr">
@@ -16921,7 +16921,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
@@ -16951,7 +16951,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C621" t="inlineStr">
@@ -16981,7 +16981,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C622" t="inlineStr">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C662" t="inlineStr">
@@ -18231,7 +18231,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -18261,7 +18261,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C665" t="inlineStr">
@@ -18321,7 +18321,7 @@
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C666" t="inlineStr">
@@ -18351,7 +18351,7 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
@@ -18381,7 +18381,7 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
@@ -18411,7 +18411,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -18441,7 +18441,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -18471,7 +18471,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -18501,7 +18501,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Mesnil st pere</t>
+          <t>Mesnil st père</t>
         </is>
       </c>
       <c r="F672" t="inlineStr">
@@ -23784,7 +23784,7 @@
           <t>Grande parcelle</t>
         </is>
       </c>
-      <c r="C878" t="inlineStr">
+      <c r="D878" t="inlineStr">
         <is>
           <t>70</t>
         </is>
@@ -23809,7 +23809,7 @@
           <t>Grande parcelle</t>
         </is>
       </c>
-      <c r="C879" t="inlineStr">
+      <c r="D879" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -23834,7 +23834,7 @@
           <t>Grande parcelle</t>
         </is>
       </c>
-      <c r="C880" t="inlineStr">
+      <c r="D880" t="inlineStr">
         <is>
           <t>55</t>
         </is>
@@ -23859,7 +23859,7 @@
           <t>Grande parcelle</t>
         </is>
       </c>
-      <c r="C881" t="inlineStr">
+      <c r="D881" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -23870,6 +23870,26 @@
         </is>
       </c>
       <c r="F881" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882">
+        <v>2026</v>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Grande parcelle</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -23975,6 +23995,106 @@
         </is>
       </c>
     </row>
+    <row r="887">
+      <c r="A887">
+        <v>2026</v>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Grande parcelle</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888">
+        <v>2026</v>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Grande parcelle</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889">
+        <v>2026</v>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Grande parcelle</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890">
+        <v>2026</v>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Grande parcelle</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
     <row r="891">
       <c r="A891">
         <v>2026</v>
@@ -24195,6 +24315,31 @@
         </is>
       </c>
     </row>
+    <row r="900">
+      <c r="A900">
+        <v>2026</v>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
     <row r="901">
       <c r="A901">
         <v>2026</v>
@@ -24209,6 +24354,16 @@
           <t>80</t>
         </is>
       </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
     </row>
     <row r="902">
       <c r="A902">
@@ -24224,6 +24379,16 @@
           <t>60</t>
         </is>
       </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
     </row>
     <row r="903">
       <c r="A903">
@@ -24239,6 +24404,16 @@
           <t>55</t>
         </is>
       </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
     </row>
     <row r="904">
       <c r="A904">
@@ -24254,6 +24429,16 @@
           <t>65</t>
         </is>
       </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
     </row>
     <row r="905">
       <c r="A905">
@@ -24267,6 +24452,576 @@
       <c r="D905" t="inlineStr">
         <is>
           <t>70</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906">
+        <v>2026</v>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907">
+        <v>2026</v>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908">
+        <v>2026</v>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909">
+        <v>2026</v>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910">
+        <v>2026</v>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911">
+        <v>2026</v>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Gîte</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912">
+        <v>2026</v>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913">
+        <v>2026</v>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914">
+        <v>2026</v>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915">
+        <v>2026</v>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916">
+        <v>2026</v>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917">
+        <v>2026</v>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918">
+        <v>2026</v>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919">
+        <v>2026</v>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920">
+        <v>2026</v>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Gite</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921">
+        <v>2026</v>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922">
+        <v>2026</v>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923">
+        <v>2026</v>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924">
+        <v>2026</v>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925">
+        <v>2026</v>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>Parcelle regeneree</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>Reg</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926">
+        <v>2026</v>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927">
+        <v>2026</v>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928">
+        <v>2026</v>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929">
+        <v>2026</v>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Chemin blanc</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>FP</t>
         </is>
       </c>
     </row>

--- a/output/site_info_clean.xlsx
+++ b/output/site_info_clean.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J929"/>
+  <dimension ref="A1:J953"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -14996,7 +14996,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Mesnil st père2</t>
+          <t>Mesnil st père 2</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -15016,7 +15016,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Mesnil st père2</t>
+          <t>Mesnil st père 2</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Mesnil st père2</t>
+          <t>Mesnil st père 2</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -15056,7 +15056,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Mesnil st père2</t>
+          <t>Mesnil st père 2</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
@@ -15076,7 +15076,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Mesnil st père2</t>
+          <t>Mesnil st père 2</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -15096,7 +15096,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Mesnil st père2</t>
+          <t>Mesnil st père 2</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Mesnil st père2</t>
+          <t>Mesnil st père 2</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Mesnil st père2</t>
+          <t>Mesnil st père 2</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Mesnil st père2</t>
+          <t>Mesnil st père 2</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
@@ -22291,7 +22291,7 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
@@ -22341,7 +22341,7 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="C822" t="inlineStr">
@@ -22366,7 +22366,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="C823" t="inlineStr">
@@ -22391,7 +22391,7 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="C824" t="inlineStr">
@@ -22416,7 +22416,7 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="F825" t="inlineStr">
@@ -22431,7 +22431,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="F826" t="inlineStr">
@@ -22446,7 +22446,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="F827" t="inlineStr">
@@ -22461,7 +22461,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="F828" t="inlineStr">
@@ -22476,7 +22476,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="F829" t="inlineStr">
@@ -22491,7 +22491,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="F830" t="inlineStr">
@@ -22506,7 +22506,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="F831" t="inlineStr">
@@ -24101,7 +24101,7 @@
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D891" t="inlineStr">
@@ -24126,7 +24126,7 @@
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D892" t="inlineStr">
@@ -24151,7 +24151,7 @@
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D893" t="inlineStr">
@@ -24176,7 +24176,7 @@
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D894" t="inlineStr">
@@ -24201,7 +24201,7 @@
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D895" t="inlineStr">
@@ -24226,7 +24226,7 @@
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D896" t="inlineStr">
@@ -24251,7 +24251,7 @@
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D897" t="inlineStr">
@@ -24276,7 +24276,7 @@
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="E898" t="inlineStr">
@@ -24346,7 +24346,7 @@
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D901" t="inlineStr">
@@ -24371,7 +24371,7 @@
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D902" t="inlineStr">
@@ -24396,7 +24396,7 @@
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D903" t="inlineStr">
@@ -24421,7 +24421,7 @@
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D904" t="inlineStr">
@@ -24446,7 +24446,7 @@
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D905" t="inlineStr">
@@ -24479,6 +24479,11 @@
           <t>45</t>
         </is>
       </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F906" t="inlineStr">
         <is>
           <t>Reg</t>
@@ -24499,6 +24504,11 @@
           <t>40</t>
         </is>
       </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="F907" t="inlineStr">
         <is>
           <t>Reg</t>
@@ -24519,6 +24529,11 @@
           <t>100</t>
         </is>
       </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F908" t="inlineStr">
         <is>
           <t>Reg</t>
@@ -24564,6 +24579,11 @@
           <t>50</t>
         </is>
       </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F910" t="inlineStr">
         <is>
           <t>Reg</t>
@@ -24576,7 +24596,7 @@
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>Gîte</t>
+          <t>Gite</t>
         </is>
       </c>
       <c r="D911" t="inlineStr">
@@ -24709,6 +24729,11 @@
           <t>45</t>
         </is>
       </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F916" t="inlineStr">
         <is>
           <t>FP</t>
@@ -24729,6 +24754,11 @@
           <t>40</t>
         </is>
       </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="F917" t="inlineStr">
         <is>
           <t>FP</t>
@@ -24749,6 +24779,11 @@
           <t>50</t>
         </is>
       </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F918" t="inlineStr">
         <is>
           <t>FP</t>
@@ -24769,6 +24804,11 @@
           <t>50</t>
         </is>
       </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F919" t="inlineStr">
         <is>
           <t>FP</t>
@@ -25022,6 +25062,611 @@
       <c r="F929" t="inlineStr">
         <is>
           <t>FP</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930">
+        <v>2026</v>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>Mesnil st père</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931">
+        <v>2026</v>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>Mesnil st père</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932">
+        <v>2026</v>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Mesnil st père</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933">
+        <v>2026</v>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Mesnil st père</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934">
+        <v>2026</v>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Mesnil st père</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935">
+        <v>2026</v>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>Mesnil st père</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936">
+        <v>2026</v>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>Mesnil st père</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937">
+        <v>2026</v>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>Mesnil st père</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+      <c r="J937" t="inlineStr">
+        <is>
+          <t>Oui</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938">
+        <v>2026</v>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Mesnil st père</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939">
+        <v>2026</v>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>Mesnil st père</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940">
+        <v>2026</v>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>Mesnil st père</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941">
+        <v>2026</v>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>Mesnil st père</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942">
+        <v>2026</v>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>Mesnil st père 2</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943">
+        <v>2026</v>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>Mesnil st père 2</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944">
+        <v>2026</v>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>Mesnil st père 2</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945">
+        <v>2026</v>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>Mesnil st père 2</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946">
+        <v>2026</v>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>Mesnil st père 2</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947">
+        <v>2026</v>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>Mesnil st père 2</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948">
+        <v>2026</v>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Mesnil st père 2</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949">
+        <v>2026</v>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Mesnil st père 2</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950">
+        <v>2026</v>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>Mesnil st père 2</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951">
+        <v>2026</v>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>Mesnil st père 2</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952">
+        <v>2026</v>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>Mesnil st père 2</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953">
+        <v>2026</v>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>Mesnil st père 2</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>FT</t>
         </is>
       </c>
     </row>

--- a/output/site_info_clean.xlsx
+++ b/output/site_info_clean.xlsx
@@ -382,7 +382,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Mode_de_gestion</t>
+          <t>Mode_de_gestion</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
